--- a/Excel/v5/UKRR DataSet Amendments.xlsx
+++ b/Excel/v5/UKRR DataSet Amendments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marta.badji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6DAA98-A7E1-4D59-B308-8B0EB5A8A071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FA16CD-AE2F-40AF-962C-0F865BCEA8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -264,9 +264,6 @@
     <t>N1</t>
   </si>
   <si>
-    <t>Canadian Study of Health and Aging Clinical Frailty Scale score (Rockwell score)</t>
-  </si>
-  <si>
     <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
   </si>
   <si>
@@ -298,9 +295,6 @@
   </si>
   <si>
     <t>Glomerular filtration rate (GFR) predicted by creatinine based formula (CKD-EPI) WITHOUT ethnicity</t>
-  </si>
-  <si>
-    <t>mL/min/1.72m^2</t>
   </si>
   <si>
     <t>Unit of measure added</t>
@@ -521,6 +515,12 @@
   </si>
   <si>
     <t>Date of assessment end</t>
+  </si>
+  <si>
+    <t>Canadian Study of Health and Aging Clinical Frailty Scale score (Rockwood score)</t>
+  </si>
+  <si>
+    <t>mL/min/1.73m^2</t>
   </si>
 </sst>
 </file>
@@ -854,24 +854,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -921,6 +903,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1376,28 +1376,28 @@
         <v>5.2</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="G4" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="42"/>
-      <c r="J4" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="K4" s="58" t="s">
-        <v>143</v>
+      <c r="J4" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -1407,55 +1407,55 @@
       <c r="B5" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="59" t="s">
+      <c r="C5" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="60" t="s">
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="61"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5.2</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="59" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="66" t="s">
+      <c r="G6" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="F6" s="67" t="s">
+      <c r="H6" s="63"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="K6" s="37" t="s">
         <v>151</v>
-      </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="K6" s="37" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
@@ -1485,7 +1485,7 @@
       <c r="J7" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="51" t="s">
+      <c r="K7" s="69" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       <c r="J8" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="52"/>
+      <c r="K8" s="70"/>
     </row>
     <row r="9" spans="1:11" ht="155" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -1545,7 +1545,7 @@
       <c r="J9" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="52"/>
+      <c r="K9" s="70"/>
     </row>
     <row r="10" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -1574,7 +1574,7 @@
       <c r="J10" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="52"/>
+      <c r="K10" s="70"/>
     </row>
     <row r="11" spans="1:11" ht="93" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -1601,7 +1601,7 @@
       <c r="J11" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="52"/>
+      <c r="K11" s="70"/>
     </row>
     <row r="12" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -1626,7 +1626,7 @@
       <c r="J12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="52"/>
+      <c r="K12" s="70"/>
     </row>
     <row r="13" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -1653,7 +1653,7 @@
       <c r="J13" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="52"/>
+      <c r="K13" s="70"/>
     </row>
     <row r="14" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -1680,7 +1680,7 @@
       <c r="J14" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K14" s="52"/>
+      <c r="K14" s="70"/>
     </row>
     <row r="15" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -1709,7 +1709,7 @@
       <c r="J15" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K15" s="52"/>
+      <c r="K15" s="70"/>
     </row>
     <row r="16" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -1736,7 +1736,7 @@
       <c r="J16" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K16" s="52"/>
+      <c r="K16" s="70"/>
     </row>
     <row r="17" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17">
@@ -1761,7 +1761,7 @@
       <c r="J17" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="K17" s="53"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A18">
@@ -1790,7 +1790,7 @@
       <c r="J18" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K18" s="54" t="s">
+      <c r="K18" s="72" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       <c r="J19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="55"/>
+      <c r="K19" s="73"/>
     </row>
     <row r="20" spans="1:11" ht="155" x14ac:dyDescent="0.35">
       <c r="A20">
@@ -1850,7 +1850,7 @@
       <c r="J20" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="55"/>
+      <c r="K20" s="73"/>
     </row>
     <row r="21" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21">
@@ -1877,7 +1877,7 @@
       <c r="J21" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="55"/>
+      <c r="K21" s="73"/>
     </row>
     <row r="22" spans="1:11" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A22">
@@ -1904,7 +1904,7 @@
       <c r="J22" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="55"/>
+      <c r="K22" s="73"/>
     </row>
     <row r="23" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23">
@@ -1929,14 +1929,14 @@
       <c r="J23" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="K23" s="56"/>
+      <c r="K23" s="74"/>
     </row>
     <row r="24" spans="1:11" ht="114.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>5.2</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>65</v>
@@ -1949,7 +1949,7 @@
         <v>40</v>
       </c>
       <c r="G24" s="49" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
@@ -1957,7 +1957,7 @@
         <v>42</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="31" x14ac:dyDescent="0.35">
@@ -1985,8 +1985,8 @@
       <c r="J25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="K25" s="55" t="s">
-        <v>132</v>
+      <c r="K25" s="73" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
@@ -2016,7 +2016,7 @@
       <c r="J26" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="K26" s="55"/>
+      <c r="K26" s="73"/>
     </row>
     <row r="27" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -2043,7 +2043,7 @@
       <c r="J27" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="K27" s="55"/>
+      <c r="K27" s="73"/>
     </row>
     <row r="28" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28">
@@ -2068,7 +2068,7 @@
       <c r="J28" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="K28" s="56"/>
+      <c r="K28" s="74"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
@@ -2087,15 +2087,15 @@
         <v>73</v>
       </c>
       <c r="F29" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K29" s="6"/>
     </row>
@@ -2104,28 +2104,28 @@
         <v>5.2</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="40" t="s">
         <v>78</v>
-      </c>
-      <c r="F30" s="40" t="s">
-        <v>79</v>
       </c>
       <c r="G30" s="41"/>
       <c r="H30" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I30" s="42"/>
       <c r="J30" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="K30" s="45" t="s">
         <v>81</v>
-      </c>
-      <c r="K30" s="45" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="31" x14ac:dyDescent="0.35">
@@ -2133,28 +2133,28 @@
         <v>5.2</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D31" s="46"/>
       <c r="E31" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="43" t="s">
         <v>84</v>
-      </c>
-      <c r="F31" s="43" t="s">
-        <v>85</v>
       </c>
       <c r="G31" s="41"/>
       <c r="H31" s="10" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="I31" s="42"/>
       <c r="J31" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="31" x14ac:dyDescent="0.35">
@@ -2162,28 +2162,28 @@
         <v>5.2</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" s="46"/>
       <c r="E32" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G32" s="41"/>
       <c r="H32" s="10" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="I32" s="42"/>
       <c r="J32" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K32" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -2191,28 +2191,28 @@
         <v>5.2</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D33" s="46"/>
       <c r="E33" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G33" s="41"/>
       <c r="H33" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -2220,28 +2220,28 @@
         <v>5.2</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D34" s="46"/>
       <c r="E34" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G34" s="41"/>
       <c r="H34" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I34" s="42"/>
       <c r="J34" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K34" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -2249,28 +2249,28 @@
         <v>5.2</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D35" s="46"/>
       <c r="E35" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G35" s="41"/>
       <c r="H35" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I35" s="42"/>
       <c r="J35" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -2278,28 +2278,28 @@
         <v>5.2</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D36" s="46"/>
       <c r="E36" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G36" s="41"/>
       <c r="H36" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I36" s="42"/>
       <c r="J36" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -2307,28 +2307,28 @@
         <v>5.2</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D37" s="46"/>
       <c r="E37" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G37" s="41"/>
       <c r="H37" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I37" s="42"/>
       <c r="J37" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -2336,32 +2336,32 @@
         <v>5.2</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D38" s="46"/>
       <c r="E38" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G38" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="H38" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G38" s="41" t="s">
+      <c r="I38" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I38" s="42" t="s">
-        <v>112</v>
-      </c>
       <c r="J38" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="31" x14ac:dyDescent="0.35">
@@ -2369,26 +2369,26 @@
         <v>5.2</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D39" s="71"/>
-      <c r="E39" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="65"/>
+      <c r="E39" s="66" t="s">
         <v>37</v>
       </c>
       <c r="F39" s="46" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G39" s="40"/>
       <c r="H39" s="40"/>
       <c r="I39" s="10"/>
       <c r="J39" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="K39" s="58" t="s">
-        <v>157</v>
+        <v>154</v>
+      </c>
+      <c r="K39" s="52" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -2398,21 +2398,21 @@
       <c r="B40" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="73" t="s">
-        <v>158</v>
+      <c r="C40" s="67" t="s">
+        <v>156</v>
       </c>
       <c r="D40" s="12"/>
-      <c r="E40" s="74" t="s">
+      <c r="E40" s="68" t="s">
         <v>37</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="G40" s="61"/>
-      <c r="H40" s="62"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="63" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="G40" s="55"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57" t="s">
+        <v>154</v>
       </c>
       <c r="K40" s="23"/>
     </row>
@@ -2421,10 +2421,10 @@
         <v>5.2</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
@@ -2434,7 +2434,7 @@
       <c r="I41" s="12"/>
       <c r="J41" s="12"/>
       <c r="K41" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -2442,10 +2442,10 @@
         <v>5.2</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12"/>
@@ -2455,7 +2455,7 @@
       <c r="I42" s="12"/>
       <c r="J42" s="12"/>
       <c r="K42" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -2463,10 +2463,10 @@
         <v>5.2</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
@@ -2476,7 +2476,7 @@
       <c r="I43" s="12"/>
       <c r="J43" s="12"/>
       <c r="K43" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -2484,10 +2484,10 @@
         <v>5.2</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
@@ -2497,7 +2497,7 @@
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
       <c r="K44" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="31" x14ac:dyDescent="0.35">
@@ -2505,10 +2505,10 @@
         <v>5.2</v>
       </c>
       <c r="B45" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
@@ -2518,7 +2518,7 @@
       <c r="I45" s="12"/>
       <c r="J45" s="12"/>
       <c r="K45" s="48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -2526,10 +2526,10 @@
         <v>5.2</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D46" s="26"/>
       <c r="E46" s="26"/>
@@ -2545,10 +2545,10 @@
         <v>5.2</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D47" s="26"/>
       <c r="E47" s="26"/>
@@ -2564,10 +2564,10 @@
         <v>5.2</v>
       </c>
       <c r="B48" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="27" t="s">
         <v>124</v>
-      </c>
-      <c r="C48" s="27" t="s">
-        <v>126</v>
       </c>
       <c r="D48" s="26"/>
       <c r="E48" s="26"/>
@@ -2580,17 +2580,17 @@
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B52" s="39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
